--- a/artfynd/A 32121-2021 artfynd.xlsx
+++ b/artfynd/A 32121-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32121-2021 artfynd.xlsx
+++ b/artfynd/A 32121-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103088425</v>
+        <v>103088395</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697961.4723919332</v>
+        <v>698020</v>
       </c>
       <c r="R2" t="n">
-        <v>7409896.450042367</v>
+        <v>7409874</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103088411</v>
+        <v>103088410</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698000.2131633657</v>
+        <v>697946</v>
       </c>
       <c r="R3" t="n">
-        <v>7409854.827216402</v>
+        <v>7409848</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103088406</v>
+        <v>103088411</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697962.0587768484</v>
+        <v>698000</v>
       </c>
       <c r="R4" t="n">
-        <v>7409866.349143908</v>
+        <v>7409855</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103089951</v>
+        <v>103088414</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697969.6287040099</v>
+        <v>697958</v>
       </c>
       <c r="R5" t="n">
-        <v>7409739.576767351</v>
+        <v>7409788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103088416</v>
+        <v>103088415</v>
       </c>
       <c r="B6" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697935.9933518639</v>
+        <v>697926</v>
       </c>
       <c r="R6" t="n">
-        <v>7409781.967319893</v>
+        <v>7409786</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103088398</v>
+        <v>103089953</v>
       </c>
       <c r="B7" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697954.5216593083</v>
+        <v>697999</v>
       </c>
       <c r="R7" t="n">
-        <v>7409910.226185078</v>
+        <v>7409783</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103088427</v>
+        <v>103089954</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697961.4723919332</v>
+        <v>698018</v>
       </c>
       <c r="R8" t="n">
-        <v>7409896.450042367</v>
+        <v>7409794</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1325,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103088431</v>
+        <v>110049846</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Klubbudden, Lu lm</t>
+          <t>Siunavare outrett, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697945.0090707223</v>
+        <v>697954</v>
       </c>
       <c r="R9" t="n">
-        <v>7409800.070442414</v>
+        <v>7409686</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,49 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103088389</v>
+        <v>103088379</v>
       </c>
       <c r="B10" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697963.5409767251</v>
+        <v>697969</v>
       </c>
       <c r="R10" t="n">
-        <v>7409807.358614104</v>
+        <v>7409775</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,19 +1519,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103088430</v>
+        <v>103088372</v>
       </c>
       <c r="B11" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697950.1523879871</v>
+        <v>697964</v>
       </c>
       <c r="R11" t="n">
-        <v>7409866.28228436</v>
+        <v>7409715</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,19 +1616,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103088414</v>
+        <v>103088413</v>
       </c>
       <c r="B12" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697957.7708358243</v>
+        <v>697958</v>
       </c>
       <c r="R12" t="n">
-        <v>7409788.300001025</v>
+        <v>7409788</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,19 +1713,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103088432</v>
+        <v>103088417</v>
       </c>
       <c r="B13" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698023.183286516</v>
+        <v>697936</v>
       </c>
       <c r="R13" t="n">
-        <v>7409850.140980494</v>
+        <v>7409782</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1980,19 +1810,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103088404</v>
+        <v>103088431</v>
       </c>
       <c r="B14" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697954.4768510704</v>
+        <v>697945</v>
       </c>
       <c r="R14" t="n">
-        <v>7409894.358200374</v>
+        <v>7409800</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,19 +1907,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103089952</v>
+        <v>103089951</v>
       </c>
       <c r="B15" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697978.6525514234</v>
+        <v>697970</v>
       </c>
       <c r="R15" t="n">
-        <v>7409746.574936721</v>
+        <v>7409740</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2204,19 +2004,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103088409</v>
+        <v>103088398</v>
       </c>
       <c r="B16" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697962.0587768484</v>
+        <v>697954</v>
       </c>
       <c r="R16" t="n">
-        <v>7409866.349143908</v>
+        <v>7409910</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2316,19 +2101,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103088426</v>
+        <v>103088404</v>
       </c>
       <c r="B17" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697961.4723919332</v>
+        <v>697954</v>
       </c>
       <c r="R17" t="n">
-        <v>7409896.450042367</v>
+        <v>7409894</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2428,19 +2198,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103088403</v>
+        <v>103088407</v>
       </c>
       <c r="B18" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697954.4768510704</v>
+        <v>697962</v>
       </c>
       <c r="R18" t="n">
-        <v>7409894.358200374</v>
+        <v>7409866</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2540,19 +2295,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103088408</v>
+        <v>103088425</v>
       </c>
       <c r="B19" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697962.0587768484</v>
+        <v>697961</v>
       </c>
       <c r="R19" t="n">
-        <v>7409866.349143908</v>
+        <v>7409896</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2652,19 +2392,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103088372</v>
+        <v>103088388</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697963.8339712686</v>
+        <v>697966</v>
       </c>
       <c r="R20" t="n">
-        <v>7409715.359528334</v>
+        <v>7409811</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2764,19 +2489,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103089955</v>
+        <v>103088402</v>
       </c>
       <c r="B21" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698004.1059550372</v>
+        <v>697938</v>
       </c>
       <c r="R21" t="n">
-        <v>7409855.901745311</v>
+        <v>7409925</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2876,19 +2586,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103088413</v>
+        <v>103088422</v>
       </c>
       <c r="B22" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697957.7708358243</v>
+        <v>697925</v>
       </c>
       <c r="R22" t="n">
-        <v>7409788.300001025</v>
+        <v>7409705</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2988,19 +2683,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103088407</v>
+        <v>103088389</v>
       </c>
       <c r="B23" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>3242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697962.0587768484</v>
+        <v>697964</v>
       </c>
       <c r="R23" t="n">
-        <v>7409866.349143908</v>
+        <v>7409807</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3100,19 +2780,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103088395</v>
+        <v>103088400</v>
       </c>
       <c r="B24" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698019.8641071836</v>
+        <v>697938</v>
       </c>
       <c r="R24" t="n">
-        <v>7409874.095309931</v>
+        <v>7409925</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3212,19 +2877,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103088387</v>
+        <v>103088403</v>
       </c>
       <c r="B25" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697965.6258612617</v>
+        <v>697954</v>
       </c>
       <c r="R25" t="n">
-        <v>7409811.475548876</v>
+        <v>7409894</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3324,19 +2974,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103088397</v>
+        <v>103088406</v>
       </c>
       <c r="B26" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697954.5216593083</v>
+        <v>697962</v>
       </c>
       <c r="R26" t="n">
-        <v>7409910.226185078</v>
+        <v>7409866</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3436,19 +3071,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103088379</v>
+        <v>103088426</v>
       </c>
       <c r="B27" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697969.0952645764</v>
+        <v>697961</v>
       </c>
       <c r="R27" t="n">
-        <v>7409774.44253059</v>
+        <v>7409896</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3548,19 +3168,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103088429</v>
+        <v>103088397</v>
       </c>
       <c r="B28" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697963.8178214509</v>
+        <v>697954</v>
       </c>
       <c r="R28" t="n">
-        <v>7409891.463420899</v>
+        <v>7409910</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3660,19 +3265,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103088394</v>
+        <v>103088421</v>
       </c>
       <c r="B29" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3715,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697969.9625860619</v>
+        <v>697925</v>
       </c>
       <c r="R29" t="n">
-        <v>7409707.472678185</v>
+        <v>7409705</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3772,19 +3362,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103088410</v>
+        <v>103089955</v>
       </c>
       <c r="B30" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3827,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697946.3002227815</v>
+        <v>698004</v>
       </c>
       <c r="R30" t="n">
-        <v>7409848.155895144</v>
+        <v>7409856</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3884,19 +3459,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,19 +3488,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>103088412</v>
+        <v>103088408</v>
       </c>
       <c r="B31" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3963,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>698011.9158672926</v>
+        <v>697962</v>
       </c>
       <c r="R31" t="n">
-        <v>7409863.208714964</v>
+        <v>7409866</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3996,19 +3556,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,37 +3585,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103088378</v>
+        <v>103088412</v>
       </c>
       <c r="B32" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697972.3407215901</v>
+        <v>698012</v>
       </c>
       <c r="R32" t="n">
-        <v>7409773.487075427</v>
+        <v>7409863</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4108,19 +3653,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103088388</v>
+        <v>103088424</v>
       </c>
       <c r="B33" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697965.6258612617</v>
+        <v>697943</v>
       </c>
       <c r="R33" t="n">
-        <v>7409811.475548876</v>
+        <v>7409922</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4220,19 +3750,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,15 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103088417</v>
+        <v>103088427</v>
       </c>
       <c r="B34" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697935.9933518639</v>
+        <v>697961</v>
       </c>
       <c r="R34" t="n">
-        <v>7409781.967319893</v>
+        <v>7409896</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4332,19 +3847,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,53 +3876,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110049846</v>
+        <v>103088416</v>
       </c>
       <c r="B35" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Siunavare outrett, Lu lm</t>
+          <t>Klubbudden, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697954.4311014272</v>
+        <v>697936</v>
       </c>
       <c r="R35" t="n">
-        <v>7409686.121686925</v>
+        <v>7409782</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4441,22 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4471,15 +3961,1082 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>103088387</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>697966</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7409811</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>103088409</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>697962</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7409866</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>103088394</v>
+      </c>
+      <c r="B38" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>697970</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7409707</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>103088429</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>697964</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7409891</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>103088373</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>697980</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7409721</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>103088374</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>697987</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7409734</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>103088378</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>697972</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7409773</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>103089952</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>697979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7409747</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>103088399</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>697928</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7409645</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>103088430</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>697950</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7409866</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>103088432</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Klubbudden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>698023</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7409850</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
